--- a/POI_List_Voucher Service.xlsx
+++ b/POI_List_Voucher Service.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\Desktop\2026_09_07\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026_09_07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C6538D-AD92-4D9B-A02E-E112905277DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E758CFDA-848C-4ABB-AD07-C5184F5052DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7226,7 +7226,7 @@
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="32.42578125" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
